--- a/data/render_parts.xlsx
+++ b/data/render_parts.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U109"/>
+  <dimension ref="A1:U139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1088,37 +1088,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply header</t>
+          <t>Lower plenum panel A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="F9" t="n">
-        <v>1120</v>
+        <v>-1090</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J9" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1151,11 +1151,7 @@
       <c r="T9" t="n">
         <v>6</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>DN150 glycol supply header</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1165,37 +1161,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Return header</t>
+          <t>Lower plenum panel B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>950</v>
+        <v>650</v>
       </c>
       <c r="F10" t="n">
-        <v>1120</v>
+        <v>1090</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J10" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1219,7 +1215,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1233,42 +1229,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MEC-001</t>
+          <t>MEC-005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Base rails</t>
+          <t>Supply header</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="G11" t="n">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1292,7 +1288,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1301,47 +1297,51 @@
       <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>DN150 glycol supply header</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MEC-001</t>
+          <t>MEC-005</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V-coil left</t>
+          <t>Return header</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vpanel</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="F12" t="n">
-        <v>-560</v>
+        <v>1120</v>
       </c>
       <c r="G12" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1374,11 +1374,7 @@
       <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Condenser coils occupy ~8.2 m of length; compressor end clear</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1388,31 +1384,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V-coil right</t>
+          <t>Base rails</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vpanel</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1300</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>8200</v>
+        <v>11900</v>
       </c>
       <c r="H13" t="n">
-        <v>70</v>
+        <v>2200</v>
       </c>
       <c r="I13" t="n">
-        <v>1750</v>
+        <v>180</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1432,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1442,7 +1438,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1461,40 +1457,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Condenser fans</t>
+          <t>V-coil left</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>vpanel</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-5050</v>
+        <v>-1800</v>
       </c>
       <c r="E14" t="n">
-        <v>2230</v>
+        <v>1300</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-560</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="J14" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1502,10 +1498,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1515,18 +1511,18 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>6</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>6 fans over coil section</t>
+          <t>Condenser coils occupy ~8.2 m of length; compressor end clear</t>
         </is>
       </c>
     </row>
@@ -1538,31 +1534,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Control panel</t>
+          <t>V-coil right</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>vpanel</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5300</v>
+        <v>-1800</v>
       </c>
       <c r="E15" t="n">
-        <v>1050</v>
+        <v>1300</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="G15" t="n">
-        <v>900</v>
+        <v>8200</v>
       </c>
       <c r="H15" t="n">
-        <v>2200</v>
+        <v>70</v>
       </c>
       <c r="I15" t="n">
-        <v>1900</v>
+        <v>1750</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1582,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1592,7 +1588,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1601,11 +1597,7 @@
       <c r="T15" t="n">
         <v>6</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Unit-mounted control/starter cabinet at end</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1615,22 +1607,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Screw compressor A</t>
+          <t>Condenser fans</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4200</v>
+        <v>-5050</v>
       </c>
       <c r="E16" t="n">
-        <v>750</v>
+        <v>2230</v>
       </c>
       <c r="F16" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1642,13 +1634,13 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>520</v>
+        <v>800</v>
       </c>
       <c r="K16" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1656,7 +1648,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1669,18 +1661,18 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>6</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Twin 06T-class screw compressors</t>
+          <t>6 fans over coil section</t>
         </is>
       </c>
     </row>
@@ -1692,37 +1684,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Screw compressor B</t>
+          <t>Control panel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4200</v>
+        <v>5300</v>
       </c>
       <c r="E17" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="F17" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J17" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -1746,7 +1738,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -1755,7 +1747,11 @@
       <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Unit-mounted control/starter cabinet at end</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1765,19 +1761,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oil separator A</t>
+          <t>Screw compressor A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="F18" t="n">
         <v>-500</v>
@@ -1792,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>420</v>
+        <v>520</v>
       </c>
       <c r="K18" t="n">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -1819,7 +1815,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -1828,7 +1824,11 @@
       <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Twin 06T-class screw compressors</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1838,19 +1838,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Oil separator B</t>
+          <t>Screw compressor B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="F19" t="n">
         <v>500</v>
@@ -1865,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>420</v>
+        <v>520</v>
       </c>
       <c r="K19" t="n">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evaporator shell</t>
+          <t>Oil separator A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1000</v>
+        <v>3300</v>
       </c>
       <c r="E20" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="K20" t="n">
-        <v>6500</v>
+        <v>1300</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -1974,11 +1974,7 @@
       <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Flooded evaporator barrel under coils</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1988,22 +1984,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHW supply stub</t>
+          <t>Oil separator B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2200</v>
+        <v>3300</v>
       </c>
       <c r="E21" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>1180</v>
+        <v>500</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2015,10 +2011,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>219</v>
+        <v>420</v>
       </c>
       <c r="K21" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -2035,14 +2031,14 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2061,7 +2057,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHW return stub</t>
+          <t>Evaporator shell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2070,13 +2066,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3000</v>
+        <v>1000</v>
       </c>
       <c r="E22" t="n">
         <v>650</v>
       </c>
       <c r="F22" t="n">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2088,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>219</v>
+        <v>900</v>
       </c>
       <c r="K22" t="n">
-        <v>400</v>
+        <v>6500</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -2108,14 +2104,14 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2124,17 +2120,21 @@
       <c r="T22" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Flooded evaporator barrel under coils</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Base frame</t>
+          <t>Lower plenum panel A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2143,22 +2143,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-1080</v>
       </c>
       <c r="G23" t="n">
-        <v>10700</v>
+        <v>8300</v>
       </c>
       <c r="H23" t="n">
-        <v>2200</v>
+        <v>60</v>
       </c>
       <c r="I23" t="n">
-        <v>180</v>
+        <v>950</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2202,12 +2202,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Body shell</t>
+          <t>Lower plenum panel B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2216,22 +2216,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E24" t="n">
-        <v>1150</v>
+        <v>600</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="G24" t="n">
-        <v>10700</v>
+        <v>8300</v>
       </c>
       <c r="H24" t="n">
-        <v>2250</v>
+        <v>60</v>
       </c>
       <c r="I24" t="n">
-        <v>1950</v>
+        <v>950</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2275,42 +2275,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Louver band left</t>
+          <t>CHW supply stub</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="E25" t="n">
-        <v>1150</v>
+        <v>650</v>
       </c>
       <c r="F25" t="n">
-        <v>-1140</v>
+        <v>1180</v>
       </c>
       <c r="G25" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2348,42 +2348,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Louver band right</t>
+          <t>CHW return stub</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="E26" t="n">
-        <v>1150</v>
+        <v>650</v>
       </c>
       <c r="F26" t="n">
-        <v>1140</v>
+        <v>1180</v>
       </c>
       <c r="G26" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -2400,14 +2400,14 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -2426,40 +2426,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fan array</t>
+          <t>Base frame</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-4450</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2320</v>
+        <v>90</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J27" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1780</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Electrical panel</t>
+          <t>Body shell</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2508,22 +2508,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>500</v>
+        <v>10700</v>
       </c>
       <c r="H28" t="n">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="I28" t="n">
-        <v>1800</v>
+        <v>1950</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -2567,12 +2567,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cold water basin</t>
+          <t>Louver band left</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2584,19 +2584,19 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>350</v>
+        <v>1150</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-1140</v>
       </c>
       <c r="G29" t="n">
-        <v>5486</v>
+        <v>10500</v>
       </c>
       <c r="H29" t="n">
-        <v>3658</v>
+        <v>50</v>
       </c>
       <c r="I29" t="n">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -2640,12 +2640,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Casing</t>
+          <t>Louver band right</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2657,19 +2657,19 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2100</v>
+        <v>1150</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="G30" t="n">
-        <v>5400</v>
+        <v>10500</v>
       </c>
       <c r="H30" t="n">
-        <v>3600</v>
+        <v>50</v>
       </c>
       <c r="I30" t="n">
-        <v>2800</v>
+        <v>1700</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>coolingTower</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -2713,45 +2713,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Air inlet louvers A</t>
+          <t>Fan array</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-4450</v>
       </c>
       <c r="E31" t="n">
-        <v>1500</v>
+        <v>2320</v>
       </c>
       <c r="F31" t="n">
-        <v>-1790</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1780</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2772,26 +2772,26 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Air inlet louvers B</t>
+          <t>Electrical panel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E32" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="F32" t="n">
-        <v>1790</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5300</v>
+        <v>500</v>
       </c>
       <c r="H32" t="n">
-        <v>60</v>
+        <v>2100</v>
       </c>
       <c r="I32" t="n">
         <v>1800</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -2864,37 +2864,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fan cylinder</t>
+          <t>Cold water basin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3900</v>
+        <v>350</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>5486</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3658</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J33" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>coolingTower</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -2927,11 +2927,7 @@
       <c r="T33" t="n">
         <v>6</v>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>FRP fan stack</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2941,34 +2937,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Axial fan</t>
+          <t>Casing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3950</v>
+        <v>2100</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="J34" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2995,20 +2991,16 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>coolingTower</t>
         </is>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>7</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Single low-speed axial fan</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3018,7 +3010,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fan motor</t>
+          <t>Air inlet louvers A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3027,22 +3019,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>4550</v>
+        <v>1500</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-1790</v>
       </c>
       <c r="G35" t="n">
-        <v>600</v>
+        <v>5300</v>
       </c>
       <c r="H35" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="I35" t="n">
-        <v>450</v>
+        <v>1800</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3072,7 +3064,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -3091,37 +3083,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hot water inlet</t>
+          <t>Air inlet louvers B</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2950</v>
+        <v>1500</v>
       </c>
       <c r="F36" t="n">
-        <v>1900</v>
+        <v>1790</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J36" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -3138,14 +3130,14 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -3159,12 +3151,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tank shell</t>
+          <t>Fan cylinder</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3176,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>10000</v>
+        <v>3900</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -3191,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>15240</v>
+        <v>2700</v>
       </c>
       <c r="K37" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -3218,7 +3210,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>coolingTower</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -3229,31 +3221,31 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Welded steel, field-erected</t>
+          <t>FRP fan stack</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Roof cone</t>
+          <t>Axial fan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>20600</v>
+        <v>3950</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3268,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>15300</v>
+        <v>2400</v>
       </c>
       <c r="K38" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -3295,70 +3287,74 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>6</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Single low-speed axial fan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ring stiffener</t>
+          <t>Fan motor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>torus</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E39" t="n">
-        <v>4000</v>
+        <v>4550</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="J39" t="n">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3377,51 +3373,47 @@
       <c r="T39" t="n">
         <v>6</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>External stiffening rings</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Access ladder</t>
+          <t>Hot water inlet</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>10500</v>
+        <v>2950</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G40" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -3438,14 +3430,14 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -3464,22 +3456,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Diffuser pipe</t>
+          <t>Tank shell</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1200</v>
+        <v>10000</v>
       </c>
       <c r="F41" t="n">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3491,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>500</v>
+        <v>15240</v>
       </c>
       <c r="K41" t="n">
-        <v>1500</v>
+        <v>20000</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -3511,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -3527,29 +3519,33 @@
       <c r="T41" t="n">
         <v>6</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Welded steel, field-erected</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tank shell</t>
+          <t>Roof cone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1800</v>
+        <v>20600</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3564,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>3000</v>
+        <v>15300</v>
       </c>
       <c r="K42" t="n">
-        <v>10400</v>
+        <v>1200</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -3591,7 +3587,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>fuelTank</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -3605,56 +3601,56 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saddle A</t>
+          <t>Ring stiffener</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>torus</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3048</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>y</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3673,17 +3669,21 @@
       <c r="T43" t="n">
         <v>6</v>
       </c>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>External stiffening rings</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saddle B</t>
+          <t>Access ladder</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3692,22 +3692,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3000</v>
+        <v>7700</v>
       </c>
       <c r="E44" t="n">
-        <v>800</v>
+        <v>10500</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H44" t="n">
-        <v>3048</v>
+        <v>450</v>
       </c>
       <c r="I44" t="n">
-        <v>1600</v>
+        <v>21000</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3751,27 +3751,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Manway</t>
+          <t>Diffuser pipe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3450</v>
+        <v>1200</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3783,10 +3783,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K45" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -3803,14 +3803,14 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -3829,19 +3829,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vent stack</t>
+          <t>Tank shell</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>4000</v>
+        <v>1800</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -3856,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="K46" t="n">
-        <v>1400</v>
+        <v>10400</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>fuelTank</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fill cabinet</t>
+          <t>Saddle A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3911,22 +3911,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-4900</v>
+        <v>-3000</v>
       </c>
       <c r="E47" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="F47" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="H47" t="n">
-        <v>500</v>
+        <v>3048</v>
       </c>
       <c r="I47" t="n">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -3965,11 +3965,7 @@
       <c r="T47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Fill/spill containment cabinet at end</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3979,7 +3975,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Level gauge</t>
+          <t>Saddle B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3988,22 +3984,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-5550</v>
+        <v>3000</v>
       </c>
       <c r="E48" t="n">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="H48" t="n">
-        <v>300</v>
+        <v>3048</v>
       </c>
       <c r="I48" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4033,7 +4029,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S48" t="n">
@@ -4047,42 +4043,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sub-base fuel tank</t>
+          <t>Manway</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>300</v>
+        <v>3450</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2438</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>600</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -4115,51 +4111,47 @@
       <c r="T49" t="n">
         <v>6</v>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Full-length UL-142 sub-base tank</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Enclosure</t>
+          <t>Vent stack</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-500</v>
+        <v>4600</v>
       </c>
       <c r="E50" t="n">
-        <v>2050</v>
+        <v>4000</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2438</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -4183,7 +4175,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>gensetEnclosure</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -4197,12 +4189,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intake louver wall</t>
+          <t>Fill cabinet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4211,22 +4203,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-6030</v>
+        <v>-4900</v>
       </c>
       <c r="E51" t="n">
-        <v>2050</v>
+        <v>1100</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H51" t="n">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="I51" t="n">
-        <v>2300</v>
+        <v>900</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4256,7 +4248,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -4267,19 +4259,19 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Cool air intake at alternator end</t>
+          <t>Fill/spill containment cabinet at end</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Side louvers</t>
+          <t>Level gauge</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4288,22 +4280,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-2500</v>
+        <v>-5550</v>
       </c>
       <c r="E52" t="n">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="F52" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>3200</v>
+        <v>120</v>
       </c>
       <c r="H52" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I52" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4333,7 +4325,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -4352,7 +4344,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Radiator discharge hood</t>
+          <t>Sub-base fuel tank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4361,22 +4353,22 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5550</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>2050</v>
+        <v>300</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1100</v>
+        <v>12000</v>
       </c>
       <c r="H53" t="n">
         <v>2438</v>
       </c>
       <c r="I53" t="n">
-        <v>2900</v>
+        <v>600</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4415,7 +4407,11 @@
       <c r="T53" t="n">
         <v>6</v>
       </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Full-length UL-142 sub-base tank</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4425,34 +4421,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Radiator fan</t>
+          <t>Enclosure</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6130</v>
+        <v>-500</v>
       </c>
       <c r="E54" t="n">
-        <v>2150</v>
+        <v>2050</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2438</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J54" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4475,24 +4471,20 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetEnclosure</t>
         </is>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>5</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Horizontal-discharge radiator fan, faces away from building</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4502,37 +4494,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Exhaust stack</t>
+          <t>Intake louver wall</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-3400</v>
+        <v>-6030</v>
       </c>
       <c r="E55" t="n">
-        <v>4750</v>
+        <v>2050</v>
       </c>
       <c r="F55" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J55" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -4556,7 +4548,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -4565,7 +4557,11 @@
       <c r="T55" t="n">
         <v>6</v>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Cool air intake at alternator end</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4575,7 +4571,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rain cap</t>
+          <t>Side louvers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4584,22 +4580,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-3400</v>
+        <v>-2500</v>
       </c>
       <c r="E56" t="n">
-        <v>5780</v>
+        <v>2300</v>
       </c>
       <c r="F56" t="n">
-        <v>500</v>
+        <v>1230</v>
       </c>
       <c r="G56" t="n">
-        <v>550</v>
+        <v>3200</v>
       </c>
       <c r="H56" t="n">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="I56" t="n">
-        <v>120</v>
+        <v>1400</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4629,7 +4625,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -4648,37 +4644,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Silencer</t>
+          <t>Radiator discharge hood</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1500</v>
+        <v>5550</v>
       </c>
       <c r="E57" t="n">
-        <v>4150</v>
+        <v>2050</v>
       </c>
       <c r="F57" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2438</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J57" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>1</v>
@@ -4702,7 +4698,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S57" t="n">
@@ -4711,11 +4707,7 @@
       <c r="T57" t="n">
         <v>6</v>
       </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Critical-grade silencer on roof</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4725,40 +4717,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Access doors</t>
+          <t>Radiator fan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-2500</v>
+        <v>6130</v>
       </c>
       <c r="E58" t="n">
-        <v>1800</v>
+        <v>2150</v>
       </c>
       <c r="F58" t="n">
-        <v>-1230</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4766,7 +4758,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -4775,20 +4767,24 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
-      </c>
-      <c r="U58" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Horizontal-discharge radiator fan, faces away from building</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4798,37 +4794,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Status beacon</t>
+          <t>Exhaust stack</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-5800</v>
+        <v>-3400</v>
       </c>
       <c r="E59" t="n">
-        <v>3650</v>
+        <v>4750</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G59" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -4852,7 +4848,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ledAmber</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -4866,12 +4862,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Skid base</t>
+          <t>Rain cap</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4880,22 +4876,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="E60" t="n">
-        <v>140</v>
+        <v>5780</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G60" t="n">
-        <v>6100</v>
+        <v>550</v>
       </c>
       <c r="H60" t="n">
-        <v>2170</v>
+        <v>550</v>
       </c>
       <c r="I60" t="n">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4939,42 +4935,42 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Engine block</t>
+          <t>Silencer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-700</v>
+        <v>-1500</v>
       </c>
       <c r="E61" t="n">
-        <v>1150</v>
+        <v>4150</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G61" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -4998,7 +4994,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>genset</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -5009,19 +5005,19 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>V16 block, CAT yellow</t>
+          <t>Critical-grade silencer on roof</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Valve covers</t>
+          <t>Access doors</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5030,22 +5026,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-700</v>
+        <v>-2500</v>
       </c>
       <c r="E62" t="n">
-        <v>2020</v>
+        <v>1800</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-1230</v>
       </c>
       <c r="G62" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="H62" t="n">
-        <v>1250</v>
+        <v>30</v>
       </c>
       <c r="I62" t="n">
-        <v>260</v>
+        <v>1800</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5054,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5062,7 +5058,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -5075,7 +5071,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>genset</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -5089,12 +5085,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Turbo + aftercooler</t>
+          <t>Status beacon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5103,22 +5099,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-2000</v>
+        <v>-5800</v>
       </c>
       <c r="E63" t="n">
-        <v>2100</v>
+        <v>3650</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="H63" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="I63" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5148,7 +5144,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>ledAmber</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -5167,37 +5163,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alternator</t>
+          <t>Skid base</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1050</v>
+        <v>140</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="J64" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>1</v>
@@ -5240,7 +5236,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Terminal box</t>
+          <t>Engine block</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5249,22 +5245,22 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2500</v>
+        <v>-700</v>
       </c>
       <c r="E65" t="n">
-        <v>1900</v>
+        <v>1150</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>700</v>
+        <v>2900</v>
       </c>
       <c r="H65" t="n">
-        <v>700</v>
+        <v>1450</v>
       </c>
       <c r="I65" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5294,7 +5290,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>genset</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -5303,7 +5299,11 @@
       <c r="T65" t="n">
         <v>6</v>
       </c>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>V16 block, CAT yellow</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Radiator</t>
+          <t>Valve covers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5322,22 +5322,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-2870</v>
+        <v>-700</v>
       </c>
       <c r="E66" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H66" t="n">
         <v>1250</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>360</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2170</v>
-      </c>
       <c r="I66" t="n">
-        <v>1950</v>
+        <v>260</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>genset</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Radiator fan</t>
+          <t>Turbo + aftercooler</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-2600</v>
+        <v>-2000</v>
       </c>
       <c r="E67" t="n">
-        <v>1250</v>
+        <v>2100</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J67" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5436,15 +5436,15 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
         <v>6</v>
@@ -5459,22 +5459,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Exhaust flex</t>
+          <t>Alternator</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-1200</v>
+        <v>1750</v>
       </c>
       <c r="E68" t="n">
-        <v>2600</v>
+        <v>1050</v>
       </c>
       <c r="F68" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -5486,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>300</v>
+        <v>1350</v>
       </c>
       <c r="K68" t="n">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -5532,37 +5532,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Air cleaner</t>
+          <t>Terminal box</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E69" t="n">
-        <v>2450</v>
+        <v>1900</v>
       </c>
       <c r="F69" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J69" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -5600,12 +5600,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Skid base</t>
+          <t>Radiator</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5614,22 +5614,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>-2870</v>
       </c>
       <c r="E70" t="n">
-        <v>150</v>
+        <v>1250</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>6800</v>
+        <v>360</v>
       </c>
       <c r="H70" t="n">
-        <v>2440</v>
+        <v>2170</v>
       </c>
       <c r="I70" t="n">
-        <v>300</v>
+        <v>1950</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -5673,39 +5673,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Engine block</t>
+          <t>Radiator fan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-800</v>
+        <v>-2600</v>
       </c>
       <c r="E71" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -5728,64 +5728,60 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>#3a5e46</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
         <v>6</v>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>QSK95 V16, Cummins green-black</t>
-        </is>
-      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Valve covers</t>
+          <t>Exhaust flex</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-800</v>
+        <v>-1200</v>
       </c>
       <c r="E72" t="n">
-        <v>2280</v>
+        <v>2600</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G72" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -5809,7 +5805,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>#3a5e46</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -5823,42 +5819,42 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Turbos</t>
+          <t>Air cleaner</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2350</v>
+        <v>2450</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G73" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>450</v>
+      </c>
+      <c r="K73" t="n">
         <v>1000</v>
-      </c>
-      <c r="I73" t="n">
-        <v>550</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -5901,37 +5897,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alternator</t>
+          <t>Skid base</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1950</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1150</v>
+        <v>150</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J74" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -5974,7 +5970,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Terminal box</t>
+          <t>Engine block</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5983,22 +5979,22 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2800</v>
+        <v>-800</v>
       </c>
       <c r="E75" t="n">
-        <v>2100</v>
+        <v>1300</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="H75" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="I75" t="n">
-        <v>550</v>
+        <v>1700</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6028,7 +6024,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>#3a5e46</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -6037,7 +6033,11 @@
       <c r="T75" t="n">
         <v>6</v>
       </c>
-      <c r="U75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>QSK95 V16, Cummins green-black</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Radiator</t>
+          <t>Valve covers</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6056,22 +6056,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E76" t="n">
+        <v>2280</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H76" t="n">
         <v>1400</v>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>400</v>
-      </c>
-      <c r="H76" t="n">
-        <v>2440</v>
-      </c>
       <c r="I76" t="n">
-        <v>2200</v>
+        <v>280</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>#3a5e46</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -6120,34 +6120,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Radiator fan</t>
+          <t>Turbos</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-2900</v>
+        <v>-2300</v>
       </c>
       <c r="E77" t="n">
-        <v>1400</v>
+        <v>2350</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="J77" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6170,15 +6170,15 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
         <v>6</v>
@@ -6193,22 +6193,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Exhaust flex</t>
+          <t>Alternator</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-1400</v>
+        <v>1950</v>
       </c>
       <c r="E78" t="n">
-        <v>2900</v>
+        <v>1150</v>
       </c>
       <c r="F78" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6220,10 +6220,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="K78" t="n">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="L78" t="n">
         <v>1</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -6261,12 +6261,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Core &amp; coil tank</t>
+          <t>Terminal box</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6275,22 +6275,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E79" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1450</v>
+        <v>800</v>
       </c>
       <c r="H79" t="n">
-        <v>1350</v>
+        <v>800</v>
       </c>
       <c r="I79" t="n">
-        <v>1850</v>
+        <v>550</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>transformer</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -6334,12 +6334,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Radiator bank A</t>
+          <t>Radiator</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6348,22 +6348,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-960</v>
+        <v>-3200</v>
       </c>
       <c r="E80" t="n">
-        <v>950</v>
+        <v>1400</v>
       </c>
       <c r="F80" t="n">
-        <v>-390</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H80" t="n">
-        <v>70</v>
+        <v>2440</v>
       </c>
       <c r="I80" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6372,15 +6372,15 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>transformerFin</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -6402,62 +6402,58 @@
       <c r="T80" t="n">
         <v>6</v>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Panel radiators, 6 per side</t>
-        </is>
-      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radiator bank B</t>
+          <t>Radiator fan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>960</v>
+        <v>-2900</v>
       </c>
       <c r="E81" t="n">
-        <v>950</v>
+        <v>1400</v>
       </c>
       <c r="F81" t="n">
-        <v>-390</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -6466,15 +6462,15 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>transformerFin</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
         <v>6</v>
@@ -6484,27 +6480,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Conservator</t>
+          <t>Exhaust flex</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E82" t="n">
-        <v>2280</v>
+        <v>2900</v>
       </c>
       <c r="F82" t="n">
-        <v>-350</v>
+        <v>450</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -6516,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>430</v>
+        <v>350</v>
       </c>
       <c r="K82" t="n">
-        <v>1350</v>
+        <v>800</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -6552,11 +6548,7 @@
       <c r="T82" t="n">
         <v>6</v>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Oil conservator drum on top</t>
-        </is>
-      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6566,40 +6558,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HV bushings</t>
+          <t>Core &amp; coil tank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F83" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1850</v>
       </c>
       <c r="J83" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -6607,7 +6599,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -6620,7 +6612,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>#e8e0cc</t>
+          <t>transformer</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -6629,11 +6621,7 @@
       <c r="T83" t="n">
         <v>6</v>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Porcelain, 3-phase</t>
-        </is>
-      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6643,48 +6631,48 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LV bushings</t>
+          <t>Radiator bank A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-350</v>
+        <v>-960</v>
       </c>
       <c r="E84" t="n">
-        <v>2320</v>
+        <v>950</v>
       </c>
       <c r="F84" t="n">
-        <v>450</v>
+        <v>-390</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J84" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>z</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -6697,7 +6685,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>#e8e0cc</t>
+          <t>transformerFin</t>
         </is>
       </c>
       <c r="S84" t="n">
@@ -6706,7 +6694,11 @@
       <c r="T84" t="n">
         <v>6</v>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Panel radiators, 6 per side</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6716,51 +6708,51 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cooling fan</t>
+          <t>Radiator bank B</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-960</v>
+        <v>960</v>
       </c>
       <c r="E85" t="n">
-        <v>300</v>
+        <v>950</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-390</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J85" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>z</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="O85" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -6770,60 +6762,56 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>transformerFin</t>
         </is>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>5</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Forced-air fan under radiator bank</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Conservator</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1000</v>
+        <v>2280</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="G86" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -6847,7 +6835,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>cdu</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -6856,50 +6844,54 @@
       <c r="T86" t="n">
         <v>6</v>
       </c>
-      <c r="U86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Oil conservator drum on top</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Front door</t>
+          <t>HV bushings</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E87" t="n">
-        <v>1050</v>
+        <v>2500</v>
       </c>
       <c r="F87" t="n">
-        <v>615</v>
+        <v>150</v>
       </c>
       <c r="G87" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -6907,7 +6899,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -6920,7 +6912,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>#e8e0cc</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -6929,50 +6921,54 @@
       <c r="T87" t="n">
         <v>6</v>
       </c>
-      <c r="U87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Porcelain, 3-phase</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HMI display</t>
+          <t>LV bushings</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="E88" t="n">
-        <v>1620</v>
+        <v>2320</v>
       </c>
       <c r="F88" t="n">
-        <v>632</v>
+        <v>450</v>
       </c>
       <c r="G88" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6980,7 +6976,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -6993,7 +6989,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>#e8e0cc</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -7007,39 +7003,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lower service grille</t>
+          <t>Cooling fan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>-960</v>
       </c>
       <c r="E89" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="F89" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7056,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -7066,16 +7062,20 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>6</v>
-      </c>
-      <c r="U89" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Forced-air fan under radiator bank</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7085,37 +7085,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TCS supply (to racks)</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>-190</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="F90" t="n">
-        <v>-680</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J90" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>1</v>
@@ -7132,14 +7132,14 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>cdu</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -7148,11 +7148,7 @@
       <c r="T90" t="n">
         <v>6</v>
       </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Blind-mate secondary loop supply</t>
-        </is>
-      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7162,37 +7158,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TCS return (from racks)</t>
+          <t>Front door</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>420</v>
+        <v>1050</v>
       </c>
       <c r="F91" t="n">
-        <v>-680</v>
+        <v>615</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J91" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>1</v>
@@ -7209,14 +7205,14 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>crahDark</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -7235,37 +7231,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FWS supply (facility)</t>
+          <t>HMI display</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-190</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>820</v>
+        <v>1620</v>
       </c>
       <c r="F92" t="n">
-        <v>-680</v>
+        <v>632</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="J92" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -7282,14 +7278,14 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -7308,37 +7304,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FWS return (facility)</t>
+          <t>Lower service grille</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>820</v>
+        <v>330</v>
       </c>
       <c r="F93" t="n">
-        <v>-680</v>
+        <v>618</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="J93" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>1</v>
@@ -7355,14 +7351,14 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -7381,37 +7377,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Status LED</t>
+          <t>TCS supply (to racks)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>260</v>
+        <v>-190</v>
       </c>
       <c r="E94" t="n">
-        <v>1850</v>
+        <v>420</v>
       </c>
       <c r="F94" t="n">
-        <v>632</v>
+        <v>-680</v>
       </c>
       <c r="G94" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L94" t="n">
         <v>1</v>
@@ -7428,14 +7424,14 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ledBlue</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -7444,47 +7440,51 @@
       <c r="T94" t="n">
         <v>6</v>
       </c>
-      <c r="U94" t="inlineStr"/>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Blind-mate secondary loop supply</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>TCS return (from racks)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E95" t="n">
-        <v>985</v>
+        <v>420</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>-680</v>
       </c>
       <c r="G95" t="n">
-        <v>2921</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>889</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1969</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -7501,14 +7501,14 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>crah</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -7522,42 +7522,42 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Discharge grille</t>
+          <t>FWS supply (facility)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>-190</v>
       </c>
       <c r="E96" t="n">
-        <v>530</v>
+        <v>820</v>
       </c>
       <c r="F96" t="n">
-        <v>455</v>
+        <v>-680</v>
       </c>
       <c r="G96" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -7574,14 +7574,14 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -7590,51 +7590,47 @@
       <c r="T96" t="n">
         <v>6</v>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Downflow front discharge</t>
-        </is>
-      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Filter access band</t>
+          <t>FWS return (facility)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E97" t="n">
-        <v>1580</v>
+        <v>820</v>
       </c>
       <c r="F97" t="n">
-        <v>455</v>
+        <v>-680</v>
       </c>
       <c r="G97" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L97" t="n">
         <v>1</v>
@@ -7651,14 +7647,14 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -7672,12 +7668,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>Status LED</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7686,22 +7682,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1180</v>
+        <v>260</v>
       </c>
       <c r="E98" t="n">
-        <v>1560</v>
+        <v>1850</v>
       </c>
       <c r="F98" t="n">
-        <v>465</v>
+        <v>632</v>
       </c>
       <c r="G98" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="H98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I98" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7731,7 +7727,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>ledBlue</t>
         </is>
       </c>
       <c r="S98" t="n">
@@ -7750,37 +7746,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CHW supply</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>300</v>
+        <v>985</v>
       </c>
       <c r="F99" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2921</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1969</v>
       </c>
       <c r="J99" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -7797,14 +7793,14 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>crah</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -7823,37 +7819,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CHW return</t>
+          <t>Discharge grille</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>300</v>
+        <v>530</v>
       </c>
       <c r="F100" t="n">
-        <v>-500</v>
+        <v>455</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="J100" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
@@ -7870,14 +7866,14 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>crahDark</t>
         </is>
       </c>
       <c r="S100" t="n">
@@ -7886,17 +7882,21 @@
       <c r="T100" t="n">
         <v>6</v>
       </c>
-      <c r="U100" t="inlineStr"/>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Downflow front discharge</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lineup body</t>
+          <t>Filter access band</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7908,19 +7908,19 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>1067</v>
+        <v>1580</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="G101" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="H101" t="n">
-        <v>991</v>
+        <v>20</v>
       </c>
       <c r="I101" t="n">
-        <v>2134</v>
+        <v>540</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>upsBody</t>
+          <t>crahDark</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -7964,12 +7964,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cabinet doors</t>
+          <t>HMI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7978,22 +7978,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>-1237</v>
+        <v>1180</v>
       </c>
       <c r="E102" t="n">
-        <v>1040</v>
+        <v>1560</v>
       </c>
       <c r="F102" t="n">
-        <v>510</v>
+        <v>465</v>
       </c>
       <c r="G102" t="n">
-        <v>780</v>
+        <v>300</v>
       </c>
       <c r="H102" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I102" t="n">
-        <v>1980</v>
+        <v>200</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8002,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>upsAccent</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -8032,51 +8032,47 @@
       <c r="T102" t="n">
         <v>6</v>
       </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>4 sections: rectifier/inverter/static switch/battery interface</t>
-        </is>
-      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HMI touchscreen</t>
+          <t>CHW supply</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-1237</v>
+        <v>-1000</v>
       </c>
       <c r="E103" t="n">
-        <v>1650</v>
+        <v>300</v>
       </c>
       <c r="F103" t="n">
-        <v>528</v>
+        <v>-500</v>
       </c>
       <c r="G103" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L103" t="n">
         <v>1</v>
@@ -8093,14 +8089,14 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -8114,42 +8110,42 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Top cable duct</t>
+          <t>CHW return</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E104" t="n">
-        <v>2210</v>
+        <v>300</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G104" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -8166,14 +8162,14 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>upsAccent</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -8192,7 +8188,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vent band</t>
+          <t>Lineup body</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8204,19 +8200,19 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>180</v>
+        <v>1067</v>
       </c>
       <c r="F105" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="H105" t="n">
-        <v>15</v>
+        <v>991</v>
       </c>
       <c r="I105" t="n">
-        <v>220</v>
+        <v>2134</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8246,7 +8242,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>upsBody</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -8260,12 +8256,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lineup body</t>
+          <t>Cabinet doors</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8274,22 +8270,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>-1237</v>
       </c>
       <c r="E106" t="n">
-        <v>985</v>
+        <v>1040</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="G106" t="n">
-        <v>5600</v>
+        <v>780</v>
       </c>
       <c r="H106" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="I106" t="n">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8298,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -8306,7 +8302,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -8319,7 +8315,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>upsBody</t>
+          <t>upsAccent</t>
         </is>
       </c>
       <c r="S106" t="n">
@@ -8328,17 +8324,21 @@
       <c r="T106" t="n">
         <v>6</v>
       </c>
-      <c r="U106" t="inlineStr"/>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>4 sections: rectifier/inverter/static switch/battery interface</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cabinet doors</t>
+          <t>HMI touchscreen</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8347,22 +8347,22 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-2330</v>
+        <v>-1237</v>
       </c>
       <c r="E107" t="n">
-        <v>960</v>
+        <v>1650</v>
       </c>
       <c r="F107" t="n">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="G107" t="n">
-        <v>880</v>
+        <v>340</v>
       </c>
       <c r="H107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I107" t="n">
-        <v>1820</v>
+        <v>220</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8371,7 +8371,7 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>upsAccent</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S107" t="n">
@@ -8401,21 +8401,17 @@
       <c r="T107" t="n">
         <v>6</v>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>6-frame lineup</t>
-        </is>
-      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>Top cable duct</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8424,22 +8420,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-2330</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>1560</v>
+        <v>2210</v>
       </c>
       <c r="F108" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>360</v>
+        <v>3300</v>
       </c>
       <c r="H108" t="n">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="I108" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8469,7 +8465,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>upsAccent</t>
         </is>
       </c>
       <c r="S108" t="n">
@@ -8483,7 +8479,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8500,58 +8496,2276 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F109" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G109" t="n">
-        <v>5500</v>
+        <v>3200</v>
       </c>
       <c r="H109" t="n">
         <v>15</v>
       </c>
       <c r="I109" t="n">
+        <v>220</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>chillerCoil</t>
+        </is>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>6</v>
+      </c>
+      <c r="U109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ELC-002</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Lineup body</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>985</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5600</v>
+      </c>
+      <c r="H110" t="n">
+        <v>970</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1970</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>upsBody</t>
+        </is>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>6</v>
+      </c>
+      <c r="U110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ELC-002</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cabinet doors</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>-2330</v>
+      </c>
+      <c r="E111" t="n">
+        <v>960</v>
+      </c>
+      <c r="F111" t="n">
+        <v>500</v>
+      </c>
+      <c r="G111" t="n">
+        <v>880</v>
+      </c>
+      <c r="H111" t="n">
+        <v>25</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1820</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>6</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>932</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>upsAccent</t>
+        </is>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>6</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>6-frame lineup</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ELC-002</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>HMI</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>-2330</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F112" t="n">
+        <v>518</v>
+      </c>
+      <c r="G112" t="n">
+        <v>360</v>
+      </c>
+      <c r="H112" t="n">
+        <v>15</v>
+      </c>
+      <c r="I112" t="n">
+        <v>230</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>screenDark</t>
+        </is>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>6</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ELC-002</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Vent band</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>170</v>
+      </c>
+      <c r="F113" t="n">
+        <v>500</v>
+      </c>
+      <c r="G113" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H113" t="n">
+        <v>15</v>
+      </c>
+      <c r="I113" t="n">
         <v>200</v>
       </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>1</v>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="inlineStr">
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="inlineStr">
         <is>
           <t>chillerCoil</t>
         </is>
       </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>6</v>
-      </c>
-      <c r="U109" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>6</v>
+      </c>
+      <c r="U113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Evaporator barrel</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>850</v>
+      </c>
+      <c r="F114" t="n">
+        <v>300</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1450</v>
+      </c>
+      <c r="K114" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>6</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Lower shell — chilled water side</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Condenser barrel</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K115" t="n">
+        <v>4500</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>6</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Upper shell — condenser water side</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Waterbox A</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>-2400</v>
+      </c>
+      <c r="E116" t="n">
+        <v>850</v>
+      </c>
+      <c r="F116" t="n">
+        <v>300</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K116" t="n">
+        <v>350</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>gensetDark</t>
+        </is>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>6</v>
+      </c>
+      <c r="U116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Waterbox B</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E117" t="n">
+        <v>850</v>
+      </c>
+      <c r="F117" t="n">
+        <v>300</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K117" t="n">
+        <v>350</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>gensetDark</t>
+        </is>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>6</v>
+      </c>
+      <c r="U117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Compressor volute</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>cyl</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>900</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K118" t="n">
+        <v>700</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>chiller</t>
+        </is>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>6</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Centrifugal compressor between shells</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Drive motor</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>850</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>chiller</t>
+        </is>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>6</v>
+      </c>
+      <c r="U119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Suction elbow</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>cyl</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2450</v>
+      </c>
+      <c r="F120" t="n">
+        <v>300</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>700</v>
+      </c>
+      <c r="K120" t="n">
+        <v>800</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>6</v>
+      </c>
+      <c r="U120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CHW nozzles</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>cyl</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>-1400</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F121" t="n">
+        <v>900</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>350</v>
+      </c>
+      <c r="K121" t="n">
+        <v>700</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>pipeSupply</t>
+        </is>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>6</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Chilled water in/out</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CDW nozzles</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>cyl</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>-1400</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>350</v>
+      </c>
+      <c r="K122" t="n">
+        <v>600</v>
+      </c>
+      <c r="L122" t="n">
+        <v>2</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>2800</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>pipeReturn</t>
+        </is>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>6</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Condenser water in/out</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MEC-003</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Control panel</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>-2100</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-900</v>
+      </c>
+      <c r="G123" t="n">
+        <v>800</v>
+      </c>
+      <c r="H123" t="n">
+        <v>300</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>pdu</t>
+        </is>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>6</v>
+      </c>
+      <c r="U123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MEC-006</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Inertia base</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>100</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H124" t="n">
+        <v>910</v>
+      </c>
+      <c r="I124" t="n">
+        <v>200</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>gensetDark</t>
+        </is>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>6</v>
+      </c>
+      <c r="U124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MEC-006</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Motor</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>-450</v>
+      </c>
+      <c r="E125" t="n">
+        <v>650</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>550</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>chiller</t>
+        </is>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>6</v>
+      </c>
+      <c r="U125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MEC-006</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Coupling guard</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>200</v>
+      </c>
+      <c r="E126" t="n">
+        <v>650</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>300</v>
+      </c>
+      <c r="K126" t="n">
+        <v>300</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>genset</t>
+        </is>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>6</v>
+      </c>
+      <c r="U126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MEC-006</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Volute casing</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>cyl</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>600</v>
+      </c>
+      <c r="E127" t="n">
+        <v>550</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>620</v>
+      </c>
+      <c r="K127" t="n">
+        <v>550</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>pipeSupply</t>
+        </is>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>6</v>
+      </c>
+      <c r="U127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MEC-006</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Suction pipe</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>950</v>
+      </c>
+      <c r="E128" t="n">
+        <v>550</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>250</v>
+      </c>
+      <c r="K128" t="n">
+        <v>650</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>pipeSupply</t>
+        </is>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>6</v>
+      </c>
+      <c r="U128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MEC-006</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Discharge pipe</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>cyl</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>600</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>200</v>
+      </c>
+      <c r="K129" t="n">
+        <v>500</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>pipeReturn</t>
+        </is>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>6</v>
+      </c>
+      <c r="U129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>LCL-004</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1132</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>600</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I130" t="n">
+        <v>2265</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>cdu</t>
+        </is>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>6</v>
+      </c>
+      <c r="U130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>LCL-004</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Front louver</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F131" t="n">
+        <v>608</v>
+      </c>
+      <c r="G131" t="n">
+        <v>540</v>
+      </c>
+      <c r="H131" t="n">
+        <v>18</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1900</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>chillerCoil</t>
+        </is>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>6</v>
+      </c>
+      <c r="U131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>LCL-004</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Internal fan column</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>fan</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>700</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-350</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>420</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>3</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>560</v>
+      </c>
+      <c r="O132" t="n">
+        <v>90</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>fanBlade</t>
+        </is>
+      </c>
+      <c r="S132" t="n">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>7</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Vertical stack of fans pulling air through the HX</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LCL-004</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Coolant supply</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>-140</v>
+      </c>
+      <c r="E133" t="n">
+        <v>300</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-660</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>76</v>
+      </c>
+      <c r="K133" t="n">
+        <v>280</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>pipeSupply</t>
+        </is>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>6</v>
+      </c>
+      <c r="U133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>LCL-004</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Coolant return</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>140</v>
+      </c>
+      <c r="E134" t="n">
+        <v>300</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-660</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>76</v>
+      </c>
+      <c r="K134" t="n">
+        <v>280</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>pipeReturn</t>
+        </is>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>6</v>
+      </c>
+      <c r="U134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>998</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>600</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>crah</t>
+        </is>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>6</v>
+      </c>
+      <c r="U135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Front discharge grille</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F136" t="n">
+        <v>558</v>
+      </c>
+      <c r="G136" t="n">
+        <v>540</v>
+      </c>
+      <c r="H136" t="n">
+        <v>18</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>crahDark</t>
+        </is>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>6</v>
+      </c>
+      <c r="U136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Rear intake grille</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-558</v>
+      </c>
+      <c r="G137" t="n">
+        <v>540</v>
+      </c>
+      <c r="H137" t="n">
+        <v>18</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>crahDark</t>
+        </is>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>6</v>
+      </c>
+      <c r="U137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HMI</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F138" t="n">
+        <v>560</v>
+      </c>
+      <c r="G138" t="n">
+        <v>220</v>
+      </c>
+      <c r="H138" t="n">
+        <v>12</v>
+      </c>
+      <c r="I138" t="n">
+        <v>140</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>screenDark</t>
+        </is>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>6</v>
+      </c>
+      <c r="U138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CHW stubs</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>cylH</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>-120</v>
+      </c>
+      <c r="E139" t="n">
+        <v>250</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-580</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>60</v>
+      </c>
+      <c r="K139" t="n">
+        <v>250</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>240</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>pipeSupply</t>
+        </is>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>6</v>
+      </c>
+      <c r="U139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/render_parts.xlsx
+++ b/data/render_parts.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U139"/>
+  <dimension ref="A1:U143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>coilSilver</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>coilSilver</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fan deck</t>
+          <t>V end closure A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-5850</v>
       </c>
       <c r="E7" t="n">
-        <v>2480</v>
+        <v>2100</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12000</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>2100</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S7" t="n">
@@ -1011,40 +1011,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC fan array</t>
+          <t>V end closure B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-5075</v>
+        <v>5850</v>
       </c>
       <c r="E8" t="n">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J8" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1065,20 +1065,16 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>8x EC axial fans, ~910 mm impeller</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lower plenum panel A</t>
+          <t>Fan deck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1100,19 +1096,19 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>650</v>
+        <v>2480</v>
       </c>
       <c r="F9" t="n">
-        <v>-1090</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>2100</v>
       </c>
       <c r="I9" t="n">
-        <v>1100</v>
+        <v>70</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1142,7 +1138,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1161,40 +1157,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lower plenum panel B</t>
+          <t>EC fan array</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-5075</v>
       </c>
       <c r="E10" t="n">
-        <v>650</v>
+        <v>2600</v>
       </c>
       <c r="F10" t="n">
-        <v>1090</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11800</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1202,7 +1198,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1215,16 +1211,20 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>8x EC axial fans, ~910 mm impeller</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1234,37 +1234,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply header</t>
+          <t>Lower plenum panel A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="F11" t="n">
-        <v>1120</v>
+        <v>-1090</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J11" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1297,11 +1297,7 @@
       <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>DN150 glycol supply header</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1311,37 +1307,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Return header</t>
+          <t>Lower plenum panel B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>950</v>
+        <v>650</v>
       </c>
       <c r="F12" t="n">
-        <v>1120</v>
+        <v>1090</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J12" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1365,7 +1361,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1379,42 +1375,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MEC-001</t>
+          <t>MEC-005</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Base rails</t>
+          <t>Supply header</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="G13" t="n">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1438,7 +1434,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1447,47 +1443,51 @@
       <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>DN150 glycol supply header</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MEC-001</t>
+          <t>MEC-005</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V-coil left</t>
+          <t>Return header</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>vpanel</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="F14" t="n">
-        <v>-560</v>
+        <v>1120</v>
       </c>
       <c r="G14" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1520,11 +1520,7 @@
       <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Condenser coils occupy ~8.2 m of length; compressor end clear</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1534,31 +1530,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V-coil right</t>
+          <t>Base rails</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vpanel</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1300</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8200</v>
+        <v>11900</v>
       </c>
       <c r="H15" t="n">
-        <v>70</v>
+        <v>2200</v>
       </c>
       <c r="I15" t="n">
-        <v>1750</v>
+        <v>180</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1578,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1588,7 +1584,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1607,40 +1603,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Condenser fans</t>
+          <t>V-coil left</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>vpanel</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-5050</v>
+        <v>-1800</v>
       </c>
       <c r="E16" t="n">
-        <v>2230</v>
+        <v>1300</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-560</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="J16" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1648,10 +1644,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1661,18 +1657,18 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>coilSilver</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>6</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>6 fans over coil section</t>
+          <t>Condenser coils occupy ~8.2 m of length; compressor end clear</t>
         </is>
       </c>
     </row>
@@ -1684,31 +1680,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Control panel</t>
+          <t>V-coil right</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>vpanel</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5300</v>
+        <v>-1800</v>
       </c>
       <c r="E17" t="n">
-        <v>1050</v>
+        <v>1300</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="G17" t="n">
-        <v>900</v>
+        <v>8200</v>
       </c>
       <c r="H17" t="n">
-        <v>2200</v>
+        <v>70</v>
       </c>
       <c r="I17" t="n">
-        <v>1900</v>
+        <v>1750</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1728,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1738,7 +1734,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>coilSilver</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -1747,11 +1743,7 @@
       <c r="T17" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Unit-mounted control/starter cabinet at end</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1761,37 +1753,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Screw compressor A</t>
+          <t>V end closure A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4200</v>
+        <v>-5850</v>
       </c>
       <c r="E18" t="n">
-        <v>750</v>
+        <v>1950</v>
       </c>
       <c r="F18" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J18" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -1815,7 +1807,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -1824,11 +1816,7 @@
       <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Twin 06T-class screw compressors</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1838,37 +1826,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Screw compressor B</t>
+          <t>V end closure B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4200</v>
+        <v>2250</v>
       </c>
       <c r="E19" t="n">
-        <v>750</v>
+        <v>1950</v>
       </c>
       <c r="F19" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J19" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1892,7 +1880,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -1911,49 +1899,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oil separator A</t>
+          <t>Condenser fans</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3300</v>
+        <v>-5050</v>
       </c>
       <c r="E20" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>800</v>
       </c>
-      <c r="F20" t="n">
-        <v>-500</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>420</v>
-      </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
         <v>1300</v>
       </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -1965,16 +1953,20 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6 fans over coil section</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1984,37 +1976,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oil separator B</t>
+          <t>Control panel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3300</v>
+        <v>5300</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="F21" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J21" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -2038,7 +2030,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2047,7 +2039,11 @@
       <c r="T21" t="n">
         <v>6</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Unit-mounted control/starter cabinet at end</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2057,7 +2053,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evaporator shell</t>
+          <t>Screw compressor A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2066,13 +2062,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1000</v>
+        <v>4200</v>
       </c>
       <c r="E22" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2084,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>900</v>
+        <v>520</v>
       </c>
       <c r="K22" t="n">
-        <v>6500</v>
+        <v>2100</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -2111,7 +2107,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2122,7 +2118,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Flooded evaporator barrel under coils</t>
+          <t>Twin 06T-class screw compressors</t>
         </is>
       </c>
     </row>
@@ -2134,37 +2130,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lower plenum panel A</t>
+          <t>Screw compressor B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1800</v>
+        <v>4200</v>
       </c>
       <c r="E23" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="F23" t="n">
-        <v>-1080</v>
+        <v>500</v>
       </c>
       <c r="G23" t="n">
-        <v>8300</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -2188,7 +2184,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -2207,37 +2203,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lower plenum panel B</t>
+          <t>Oil separator A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-1800</v>
+        <v>3300</v>
       </c>
       <c r="E24" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>1080</v>
+        <v>-500</v>
       </c>
       <c r="G24" t="n">
-        <v>8300</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -2261,7 +2257,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -2280,22 +2276,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHW supply stub</t>
+          <t>Oil separator B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-2200</v>
+        <v>3300</v>
       </c>
       <c r="E25" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>1180</v>
+        <v>500</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2307,10 +2303,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>219</v>
+        <v>420</v>
       </c>
       <c r="K25" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
@@ -2327,14 +2323,14 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -2353,7 +2349,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHW return stub</t>
+          <t>Evaporator shell</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2362,13 +2358,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-3000</v>
+        <v>1000</v>
       </c>
       <c r="E26" t="n">
         <v>650</v>
       </c>
       <c r="F26" t="n">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2380,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>219</v>
+        <v>900</v>
       </c>
       <c r="K26" t="n">
-        <v>400</v>
+        <v>6500</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -2400,14 +2396,14 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -2416,17 +2412,21 @@
       <c r="T26" t="n">
         <v>6</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Flooded evaporator barrel under coils</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Base frame</t>
+          <t>Lower plenum panel A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2435,22 +2435,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1080</v>
       </c>
       <c r="G27" t="n">
-        <v>10700</v>
+        <v>8300</v>
       </c>
       <c r="H27" t="n">
-        <v>2200</v>
+        <v>60</v>
       </c>
       <c r="I27" t="n">
-        <v>180</v>
+        <v>950</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -2494,12 +2494,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Body shell</t>
+          <t>Lower plenum panel B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2508,22 +2508,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E28" t="n">
-        <v>1150</v>
+        <v>600</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="G28" t="n">
-        <v>10700</v>
+        <v>8300</v>
       </c>
       <c r="H28" t="n">
-        <v>2250</v>
+        <v>60</v>
       </c>
       <c r="I28" t="n">
-        <v>1950</v>
+        <v>950</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -2567,42 +2567,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Louver band left</t>
+          <t>CHW supply stub</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="E29" t="n">
-        <v>1150</v>
+        <v>650</v>
       </c>
       <c r="F29" t="n">
-        <v>-1140</v>
+        <v>1180</v>
       </c>
       <c r="G29" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2619,14 +2619,14 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -2640,42 +2640,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MEC-002</t>
+          <t>MEC-001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Louver band right</t>
+          <t>CHW return stub</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="E30" t="n">
-        <v>1150</v>
+        <v>650</v>
       </c>
       <c r="F30" t="n">
-        <v>1140</v>
+        <v>1180</v>
       </c>
       <c r="G30" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -2692,14 +2692,14 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -2718,40 +2718,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fan array</t>
+          <t>Base frame</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-4450</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2320</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J31" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1780</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2772,14 +2772,14 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Electrical panel</t>
+          <t>Body shell</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2800,22 +2800,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>500</v>
+        <v>10700</v>
       </c>
       <c r="H32" t="n">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="I32" t="n">
-        <v>1800</v>
+        <v>1950</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>casing</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -2859,12 +2859,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cold water basin</t>
+          <t>Louver band left</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2876,19 +2876,19 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>350</v>
+        <v>1150</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-1140</v>
       </c>
       <c r="G33" t="n">
-        <v>5486</v>
+        <v>10500</v>
       </c>
       <c r="H33" t="n">
-        <v>3658</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>coilSilver</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -2932,12 +2932,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Casing</t>
+          <t>Louver band right</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2949,19 +2949,19 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2100</v>
+        <v>1150</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="G34" t="n">
-        <v>5400</v>
+        <v>10500</v>
       </c>
       <c r="H34" t="n">
-        <v>3600</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
-        <v>2800</v>
+        <v>1700</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>coolingTower</t>
+          <t>coilSilver</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3005,45 +3005,45 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Air inlet louvers A</t>
+          <t>Fan array</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-4450</v>
       </c>
       <c r="E35" t="n">
-        <v>1500</v>
+        <v>2320</v>
       </c>
       <c r="F35" t="n">
-        <v>-1790</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1780</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3064,26 +3064,26 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MEC-004</t>
+          <t>MEC-002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Air inlet louvers B</t>
+          <t>Electrical panel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3092,19 +3092,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E36" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="F36" t="n">
-        <v>1790</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>5300</v>
+        <v>500</v>
       </c>
       <c r="H36" t="n">
-        <v>60</v>
+        <v>2100</v>
       </c>
       <c r="I36" t="n">
         <v>1800</v>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -3156,37 +3156,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fan cylinder</t>
+          <t>Cold water basin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>3900</v>
+        <v>350</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>5486</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3658</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J37" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>coolingTower</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -3219,11 +3219,7 @@
       <c r="T37" t="n">
         <v>6</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>FRP fan stack</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3233,34 +3229,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Axial fan</t>
+          <t>Casing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3950</v>
+        <v>2100</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="J38" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3287,20 +3283,16 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>coolingTower</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Single low-speed axial fan</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3310,7 +3302,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fan motor</t>
+          <t>Air inlet louvers A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3319,22 +3311,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>4550</v>
+        <v>1500</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-1790</v>
       </c>
       <c r="G39" t="n">
-        <v>600</v>
+        <v>5300</v>
       </c>
       <c r="H39" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="I39" t="n">
-        <v>450</v>
+        <v>1800</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3364,7 +3356,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -3383,37 +3375,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hot water inlet</t>
+          <t>Air inlet louvers B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>2950</v>
+        <v>1500</v>
       </c>
       <c r="F40" t="n">
-        <v>1900</v>
+        <v>1790</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J40" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -3430,14 +3422,14 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -3451,12 +3443,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tank shell</t>
+          <t>Fan cylinder</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3468,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>10000</v>
+        <v>3900</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3483,10 +3475,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>15240</v>
+        <v>2700</v>
       </c>
       <c r="K41" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -3510,7 +3502,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>coolingTower</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -3521,31 +3513,31 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Welded steel, field-erected</t>
+          <t>FRP fan stack</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Roof cone</t>
+          <t>Axial fan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>20600</v>
+        <v>3950</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3560,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>15300</v>
+        <v>2400</v>
       </c>
       <c r="K42" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -3587,70 +3579,74 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
-      </c>
-      <c r="U42" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Single low-speed axial fan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ring stiffener</t>
+          <t>Fan motor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>torus</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E43" t="n">
-        <v>4000</v>
+        <v>4550</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="J43" t="n">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3669,51 +3665,47 @@
       <c r="T43" t="n">
         <v>6</v>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>External stiffening rings</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MEC-007</t>
+          <t>MEC-004</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Access ladder</t>
+          <t>Hot water inlet</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7700</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>10500</v>
+        <v>2950</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G44" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -3730,14 +3722,14 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -3756,22 +3748,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Diffuser pipe</t>
+          <t>Tank shell</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1200</v>
+        <v>10000</v>
       </c>
       <c r="F45" t="n">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3783,10 +3775,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>500</v>
+        <v>15240</v>
       </c>
       <c r="K45" t="n">
-        <v>1500</v>
+        <v>20000</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -3803,14 +3795,14 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S45" t="n">
@@ -3819,29 +3811,33 @@
       <c r="T45" t="n">
         <v>6</v>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Welded steel, field-erected</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tank shell</t>
+          <t>Roof cone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1800</v>
+        <v>20600</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -3856,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3000</v>
+        <v>15300</v>
       </c>
       <c r="K46" t="n">
-        <v>10400</v>
+        <v>1200</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -3883,7 +3879,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>fuelTank</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -3897,56 +3893,56 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saddle A</t>
+          <t>Ring stiffener</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>torus</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3048</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>y</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -3965,17 +3961,21 @@
       <c r="T47" t="n">
         <v>6</v>
       </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>External stiffening rings</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Saddle B</t>
+          <t>Access ladder</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3984,22 +3984,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3000</v>
+        <v>7700</v>
       </c>
       <c r="E48" t="n">
-        <v>800</v>
+        <v>10500</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H48" t="n">
-        <v>3048</v>
+        <v>450</v>
       </c>
       <c r="I48" t="n">
-        <v>1600</v>
+        <v>21000</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4043,27 +4043,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FUE-001</t>
+          <t>MEC-007</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Manway</t>
+          <t>Diffuser pipe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>3450</v>
+        <v>1200</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -4075,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K49" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -4095,14 +4095,14 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -4121,19 +4121,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vent stack</t>
+          <t>Tank shell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>4000</v>
+        <v>1800</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="K50" t="n">
-        <v>1400</v>
+        <v>10400</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>fuelTank</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fill cabinet</t>
+          <t>Saddle A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4203,22 +4203,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-4900</v>
+        <v>-3000</v>
       </c>
       <c r="E51" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="F51" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="H51" t="n">
-        <v>500</v>
+        <v>3048</v>
       </c>
       <c r="I51" t="n">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -4257,11 +4257,7 @@
       <c r="T51" t="n">
         <v>6</v>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Fill/spill containment cabinet at end</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4271,7 +4267,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Level gauge</t>
+          <t>Saddle B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4280,22 +4276,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-5550</v>
+        <v>3000</v>
       </c>
       <c r="E52" t="n">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="H52" t="n">
-        <v>300</v>
+        <v>3048</v>
       </c>
       <c r="I52" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4325,7 +4321,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -4339,42 +4335,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sub-base fuel tank</t>
+          <t>Manway</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>300</v>
+        <v>3450</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2438</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>600</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -4407,51 +4403,47 @@
       <c r="T53" t="n">
         <v>6</v>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Full-length UL-142 sub-base tank</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Enclosure</t>
+          <t>Vent stack</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-500</v>
+        <v>4600</v>
       </c>
       <c r="E54" t="n">
-        <v>2050</v>
+        <v>4000</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2438</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
@@ -4475,7 +4467,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>gensetEnclosure</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -4489,12 +4481,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Intake louver wall</t>
+          <t>Fill cabinet</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4503,22 +4495,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-6030</v>
+        <v>-4900</v>
       </c>
       <c r="E55" t="n">
-        <v>2050</v>
+        <v>1100</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G55" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H55" t="n">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="I55" t="n">
-        <v>2300</v>
+        <v>900</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4548,7 +4540,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S55" t="n">
@@ -4559,19 +4551,19 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Cool air intake at alternator end</t>
+          <t>Fill/spill containment cabinet at end</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BKP-003</t>
+          <t>FUE-001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Side louvers</t>
+          <t>Level gauge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4580,22 +4572,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-2500</v>
+        <v>-5550</v>
       </c>
       <c r="E56" t="n">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="F56" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3200</v>
+        <v>120</v>
       </c>
       <c r="H56" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I56" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4625,7 +4617,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -4644,7 +4636,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Radiator discharge hood</t>
+          <t>Sub-base fuel tank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4653,22 +4645,22 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5550</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2050</v>
+        <v>300</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1100</v>
+        <v>12000</v>
       </c>
       <c r="H57" t="n">
         <v>2438</v>
       </c>
       <c r="I57" t="n">
-        <v>2900</v>
+        <v>600</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4707,7 +4699,11 @@
       <c r="T57" t="n">
         <v>6</v>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Full-length UL-142 sub-base tank</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4717,34 +4713,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Radiator fan</t>
+          <t>Enclosure</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6130</v>
+        <v>-500</v>
       </c>
       <c r="E58" t="n">
-        <v>2150</v>
+        <v>2050</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2438</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J58" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -4767,24 +4763,20 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetEnclosure</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>5</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Horizontal-discharge radiator fan, faces away from building</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4794,37 +4786,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Exhaust stack</t>
+          <t>Intake louver wall</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-3400</v>
+        <v>-6030</v>
       </c>
       <c r="E59" t="n">
-        <v>4750</v>
+        <v>2050</v>
       </c>
       <c r="F59" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J59" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -4848,7 +4840,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -4857,7 +4849,11 @@
       <c r="T59" t="n">
         <v>6</v>
       </c>
-      <c r="U59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Cool air intake at alternator end</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4867,7 +4863,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rain cap</t>
+          <t>Side louvers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4876,22 +4872,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-3400</v>
+        <v>-2500</v>
       </c>
       <c r="E60" t="n">
-        <v>5780</v>
+        <v>2300</v>
       </c>
       <c r="F60" t="n">
-        <v>500</v>
+        <v>1230</v>
       </c>
       <c r="G60" t="n">
-        <v>550</v>
+        <v>3200</v>
       </c>
       <c r="H60" t="n">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="I60" t="n">
-        <v>120</v>
+        <v>1400</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4921,7 +4917,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -4940,37 +4936,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Silencer</t>
+          <t>Radiator discharge hood</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-1500</v>
+        <v>5550</v>
       </c>
       <c r="E61" t="n">
-        <v>4150</v>
+        <v>2050</v>
       </c>
       <c r="F61" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2438</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J61" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -4994,7 +4990,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -5003,11 +4999,7 @@
       <c r="T61" t="n">
         <v>6</v>
       </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Critical-grade silencer on roof</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5017,40 +5009,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Access doors</t>
+          <t>Radiator fan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-2500</v>
+        <v>6130</v>
       </c>
       <c r="E62" t="n">
-        <v>1800</v>
+        <v>2150</v>
       </c>
       <c r="F62" t="n">
-        <v>-1230</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5058,7 +5050,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -5067,20 +5059,24 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Horizontal-discharge radiator fan, faces away from building</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5090,37 +5086,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Status beacon</t>
+          <t>Exhaust stack</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-5800</v>
+        <v>-3400</v>
       </c>
       <c r="E63" t="n">
-        <v>3650</v>
+        <v>4750</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G63" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="L63" t="n">
         <v>1</v>
@@ -5144,7 +5140,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ledAmber</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S63" t="n">
@@ -5158,12 +5154,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Skid base</t>
+          <t>Rain cap</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5172,22 +5168,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>-3400</v>
       </c>
       <c r="E64" t="n">
-        <v>140</v>
+        <v>5780</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G64" t="n">
-        <v>6100</v>
+        <v>550</v>
       </c>
       <c r="H64" t="n">
-        <v>2170</v>
+        <v>550</v>
       </c>
       <c r="I64" t="n">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5231,42 +5227,42 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Engine block</t>
+          <t>Silencer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-700</v>
+        <v>-1500</v>
       </c>
       <c r="E65" t="n">
-        <v>1150</v>
+        <v>4150</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G65" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -5290,7 +5286,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>genset</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -5301,19 +5297,19 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>V16 block, CAT yellow</t>
+          <t>Critical-grade silencer on roof</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Valve covers</t>
+          <t>Access doors</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5322,22 +5318,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-700</v>
+        <v>-2500</v>
       </c>
       <c r="E66" t="n">
-        <v>2020</v>
+        <v>1800</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>-1230</v>
       </c>
       <c r="G66" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="H66" t="n">
-        <v>1250</v>
+        <v>30</v>
       </c>
       <c r="I66" t="n">
-        <v>260</v>
+        <v>1800</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5346,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5354,7 +5350,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -5367,7 +5363,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>genset</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -5381,12 +5377,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BKP-001</t>
+          <t>BKP-003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Turbo + aftercooler</t>
+          <t>Status beacon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5395,22 +5391,22 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-2000</v>
+        <v>-5800</v>
       </c>
       <c r="E67" t="n">
-        <v>2100</v>
+        <v>3650</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="H67" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="I67" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>ledAmber</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -5459,37 +5455,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alternator</t>
+          <t>Skid base</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1050</v>
+        <v>140</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="J68" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -5532,7 +5528,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Terminal box</t>
+          <t>Engine block</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5541,22 +5537,22 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2500</v>
+        <v>-700</v>
       </c>
       <c r="E69" t="n">
-        <v>1900</v>
+        <v>1150</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>700</v>
+        <v>2900</v>
       </c>
       <c r="H69" t="n">
-        <v>700</v>
+        <v>1450</v>
       </c>
       <c r="I69" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5586,7 +5582,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>genset</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -5595,7 +5591,11 @@
       <c r="T69" t="n">
         <v>6</v>
       </c>
-      <c r="U69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>V16 block, CAT yellow</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Radiator</t>
+          <t>Valve covers</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5614,22 +5614,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-2870</v>
+        <v>-700</v>
       </c>
       <c r="E70" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H70" t="n">
         <v>1250</v>
       </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>360</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2170</v>
-      </c>
       <c r="I70" t="n">
-        <v>1950</v>
+        <v>260</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>genset</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -5678,34 +5678,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Radiator fan</t>
+          <t>Turbo + aftercooler</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-2600</v>
+        <v>-2000</v>
       </c>
       <c r="E71" t="n">
-        <v>1250</v>
+        <v>2100</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J71" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -5728,15 +5728,15 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
         <v>6</v>
@@ -5751,22 +5751,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Exhaust flex</t>
+          <t>Alternator</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-1200</v>
+        <v>1750</v>
       </c>
       <c r="E72" t="n">
-        <v>2600</v>
+        <v>1050</v>
       </c>
       <c r="F72" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -5778,10 +5778,10 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>300</v>
+        <v>1350</v>
       </c>
       <c r="K72" t="n">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -5824,37 +5824,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Air cleaner</t>
+          <t>Terminal box</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E73" t="n">
-        <v>2450</v>
+        <v>1900</v>
       </c>
       <c r="F73" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J73" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -5892,12 +5892,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Skid base</t>
+          <t>Radiator</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5906,22 +5906,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>-2870</v>
       </c>
       <c r="E74" t="n">
-        <v>150</v>
+        <v>1250</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>6800</v>
+        <v>360</v>
       </c>
       <c r="H74" t="n">
-        <v>2440</v>
+        <v>2170</v>
       </c>
       <c r="I74" t="n">
-        <v>300</v>
+        <v>1950</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -5965,39 +5965,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Engine block</t>
+          <t>Radiator fan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-800</v>
+        <v>-2600</v>
       </c>
       <c r="E75" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -6020,64 +6020,60 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>#3a5e46</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
         <v>6</v>
       </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>QSK95 V16, Cummins green-black</t>
-        </is>
-      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Valve covers</t>
+          <t>Exhaust flex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-800</v>
+        <v>-1200</v>
       </c>
       <c r="E76" t="n">
-        <v>2280</v>
+        <v>2600</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G76" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L76" t="n">
         <v>1</v>
@@ -6101,7 +6097,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>#3a5e46</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -6115,42 +6111,42 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BKP-002</t>
+          <t>BKP-001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Turbos</t>
+          <t>Air cleaner</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>2350</v>
+        <v>2450</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G77" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>450</v>
+      </c>
+      <c r="K77" t="n">
         <v>1000</v>
-      </c>
-      <c r="I77" t="n">
-        <v>550</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
@@ -6193,37 +6189,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alternator</t>
+          <t>Skid base</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1950</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1150</v>
+        <v>150</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J78" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>1</v>
@@ -6266,7 +6262,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Terminal box</t>
+          <t>Engine block</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6275,22 +6271,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2800</v>
+        <v>-800</v>
       </c>
       <c r="E79" t="n">
-        <v>2100</v>
+        <v>1300</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="H79" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="I79" t="n">
-        <v>550</v>
+        <v>1700</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6320,7 +6316,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>#3a5e46</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -6329,7 +6325,11 @@
       <c r="T79" t="n">
         <v>6</v>
       </c>
-      <c r="U79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>QSK95 V16, Cummins green-black</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Radiator</t>
+          <t>Valve covers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6348,22 +6348,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E80" t="n">
+        <v>2280</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H80" t="n">
         <v>1400</v>
       </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>400</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2440</v>
-      </c>
       <c r="I80" t="n">
-        <v>2200</v>
+        <v>280</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>#3a5e46</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -6412,34 +6412,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radiator fan</t>
+          <t>Turbos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-2900</v>
+        <v>-2300</v>
       </c>
       <c r="E81" t="n">
-        <v>1400</v>
+        <v>2350</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="J81" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6462,15 +6462,15 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
         <v>6</v>
@@ -6485,22 +6485,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Exhaust flex</t>
+          <t>Alternator</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-1400</v>
+        <v>1950</v>
       </c>
       <c r="E82" t="n">
-        <v>2900</v>
+        <v>1150</v>
       </c>
       <c r="F82" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="K82" t="n">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -6553,12 +6553,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Core &amp; coil tank</t>
+          <t>Terminal box</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6567,22 +6567,22 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E83" t="n">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1450</v>
+        <v>800</v>
       </c>
       <c r="H83" t="n">
-        <v>1350</v>
+        <v>800</v>
       </c>
       <c r="I83" t="n">
-        <v>1850</v>
+        <v>550</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>transformer</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S83" t="n">
@@ -6626,12 +6626,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Radiator bank A</t>
+          <t>Radiator</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6640,22 +6640,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-960</v>
+        <v>-3200</v>
       </c>
       <c r="E84" t="n">
-        <v>950</v>
+        <v>1400</v>
       </c>
       <c r="F84" t="n">
-        <v>-390</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H84" t="n">
-        <v>70</v>
+        <v>2440</v>
       </c>
       <c r="I84" t="n">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6664,15 +6664,15 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>transformerFin</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S84" t="n">
@@ -6694,62 +6694,58 @@
       <c r="T84" t="n">
         <v>6</v>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Panel radiators, 6 per side</t>
-        </is>
-      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Radiator bank B</t>
+          <t>Radiator fan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>960</v>
+        <v>-2900</v>
       </c>
       <c r="E85" t="n">
-        <v>950</v>
+        <v>1400</v>
       </c>
       <c r="F85" t="n">
-        <v>-390</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -6758,15 +6754,15 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>transformerFin</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
         <v>6</v>
@@ -6776,27 +6772,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ELC-008</t>
+          <t>BKP-002</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Conservator</t>
+          <t>Exhaust flex</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E86" t="n">
-        <v>2280</v>
+        <v>2900</v>
       </c>
       <c r="F86" t="n">
-        <v>-350</v>
+        <v>450</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -6808,10 +6804,10 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>430</v>
+        <v>350</v>
       </c>
       <c r="K86" t="n">
-        <v>1350</v>
+        <v>800</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -6844,11 +6840,7 @@
       <c r="T86" t="n">
         <v>6</v>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Oil conservator drum on top</t>
-        </is>
-      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6858,40 +6850,40 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HV bushings</t>
+          <t>Core &amp; coil tank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="F87" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1850</v>
       </c>
       <c r="J87" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -6899,7 +6891,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -6912,7 +6904,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>#e8e0cc</t>
+          <t>transformer</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -6921,11 +6913,7 @@
       <c r="T87" t="n">
         <v>6</v>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Porcelain, 3-phase</t>
-        </is>
-      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6935,48 +6923,48 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LV bushings</t>
+          <t>Radiator bank A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-350</v>
+        <v>-960</v>
       </c>
       <c r="E88" t="n">
-        <v>2320</v>
+        <v>950</v>
       </c>
       <c r="F88" t="n">
-        <v>450</v>
+        <v>-390</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J88" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>z</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -6989,7 +6977,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>#e8e0cc</t>
+          <t>transformerFin</t>
         </is>
       </c>
       <c r="S88" t="n">
@@ -6998,7 +6986,11 @@
       <c r="T88" t="n">
         <v>6</v>
       </c>
-      <c r="U88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Panel radiators, 6 per side</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7008,51 +7000,51 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cooling fan</t>
+          <t>Radiator bank B</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-960</v>
+        <v>960</v>
       </c>
       <c r="E89" t="n">
-        <v>300</v>
+        <v>950</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>-390</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J89" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>z</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="O89" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -7062,60 +7054,56 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>transformerFin</t>
         </is>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>5</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Forced-air fan under radiator bank</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Conservator</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1000</v>
+        <v>2280</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="G90" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="L90" t="n">
         <v>1</v>
@@ -7139,7 +7127,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>cdu</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -7148,50 +7136,54 @@
       <c r="T90" t="n">
         <v>6</v>
       </c>
-      <c r="U90" t="inlineStr"/>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Oil conservator drum on top</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Front door</t>
+          <t>HV bushings</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E91" t="n">
-        <v>1050</v>
+        <v>2500</v>
       </c>
       <c r="F91" t="n">
-        <v>615</v>
+        <v>150</v>
       </c>
       <c r="G91" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7199,7 +7191,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -7212,7 +7204,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>#e8e0cc</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -7221,50 +7213,54 @@
       <c r="T91" t="n">
         <v>6</v>
       </c>
-      <c r="U91" t="inlineStr"/>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Porcelain, 3-phase</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HMI display</t>
+          <t>LV bushings</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="E92" t="n">
-        <v>1620</v>
+        <v>2320</v>
       </c>
       <c r="F92" t="n">
-        <v>632</v>
+        <v>450</v>
       </c>
       <c r="G92" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -7272,7 +7268,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -7285,7 +7281,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>#e8e0cc</t>
         </is>
       </c>
       <c r="S92" t="n">
@@ -7299,39 +7295,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LCL-002</t>
+          <t>ELC-008</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lower service grille</t>
+          <t>Cooling fan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>-960</v>
       </c>
       <c r="E93" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="F93" t="n">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>690</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -7348,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -7358,16 +7354,20 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="n">
-        <v>6</v>
-      </c>
-      <c r="U93" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Forced-air fan under radiator bank</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7377,37 +7377,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TCS supply (to racks)</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-190</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="F94" t="n">
-        <v>-680</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J94" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>1</v>
@@ -7424,14 +7424,14 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>cdu</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -7440,11 +7440,7 @@
       <c r="T94" t="n">
         <v>6</v>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Blind-mate secondary loop supply</t>
-        </is>
-      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7454,37 +7450,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TCS return (from racks)</t>
+          <t>Front door</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>420</v>
+        <v>1050</v>
       </c>
       <c r="F95" t="n">
-        <v>-680</v>
+        <v>615</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J95" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -7501,14 +7497,14 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>crahDark</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -7527,37 +7523,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FWS supply (facility)</t>
+          <t>HMI display</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-190</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>820</v>
+        <v>1620</v>
       </c>
       <c r="F96" t="n">
-        <v>-680</v>
+        <v>632</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="J96" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -7574,14 +7570,14 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S96" t="n">
@@ -7600,37 +7596,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FWS return (facility)</t>
+          <t>Lower service grille</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>820</v>
+        <v>330</v>
       </c>
       <c r="F97" t="n">
-        <v>-680</v>
+        <v>618</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="J97" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>1</v>
@@ -7647,14 +7643,14 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -7673,37 +7669,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Status LED</t>
+          <t>TCS supply (to racks)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>260</v>
+        <v>-190</v>
       </c>
       <c r="E98" t="n">
-        <v>1850</v>
+        <v>420</v>
       </c>
       <c r="F98" t="n">
-        <v>632</v>
+        <v>-680</v>
       </c>
       <c r="G98" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -7720,14 +7716,14 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ledBlue</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S98" t="n">
@@ -7736,47 +7732,51 @@
       <c r="T98" t="n">
         <v>6</v>
       </c>
-      <c r="U98" t="inlineStr"/>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Blind-mate secondary loop supply</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>TCS return (from racks)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E99" t="n">
-        <v>985</v>
+        <v>420</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>-680</v>
       </c>
       <c r="G99" t="n">
-        <v>2921</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>889</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1969</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -7793,14 +7793,14 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>crah</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S99" t="n">
@@ -7814,42 +7814,42 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Discharge grille</t>
+          <t>FWS supply (facility)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>-190</v>
       </c>
       <c r="E100" t="n">
-        <v>530</v>
+        <v>820</v>
       </c>
       <c r="F100" t="n">
-        <v>455</v>
+        <v>-680</v>
       </c>
       <c r="G100" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
@@ -7866,14 +7866,14 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S100" t="n">
@@ -7882,51 +7882,47 @@
       <c r="T100" t="n">
         <v>6</v>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Downflow front discharge</t>
-        </is>
-      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Filter access band</t>
+          <t>FWS return (facility)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E101" t="n">
-        <v>1580</v>
+        <v>820</v>
       </c>
       <c r="F101" t="n">
-        <v>455</v>
+        <v>-680</v>
       </c>
       <c r="G101" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -7943,14 +7939,14 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -7964,12 +7960,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ACL-002</t>
+          <t>LCL-002</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>Status LED</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7978,22 +7974,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1180</v>
+        <v>260</v>
       </c>
       <c r="E102" t="n">
-        <v>1560</v>
+        <v>1850</v>
       </c>
       <c r="F102" t="n">
-        <v>465</v>
+        <v>632</v>
       </c>
       <c r="G102" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="H102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I102" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8023,7 +8019,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>ledBlue</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -8042,37 +8038,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CHW supply</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>300</v>
+        <v>985</v>
       </c>
       <c r="F103" t="n">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>2921</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1969</v>
       </c>
       <c r="J103" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
         <v>1</v>
@@ -8089,14 +8085,14 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>crah</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -8115,37 +8111,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CHW return</t>
+          <t>Discharge grille</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>300</v>
+        <v>530</v>
       </c>
       <c r="F104" t="n">
-        <v>-500</v>
+        <v>455</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="J104" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -8162,14 +8158,14 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>crahDark</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -8178,17 +8174,21 @@
       <c r="T104" t="n">
         <v>6</v>
       </c>
-      <c r="U104" t="inlineStr"/>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Downflow front discharge</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lineup body</t>
+          <t>Filter access band</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8200,19 +8200,19 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>1067</v>
+        <v>1580</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="G105" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="H105" t="n">
-        <v>991</v>
+        <v>20</v>
       </c>
       <c r="I105" t="n">
-        <v>2134</v>
+        <v>540</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>upsBody</t>
+          <t>crahDark</t>
         </is>
       </c>
       <c r="S105" t="n">
@@ -8256,12 +8256,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cabinet doors</t>
+          <t>HMI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8270,22 +8270,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-1237</v>
+        <v>1180</v>
       </c>
       <c r="E106" t="n">
-        <v>1040</v>
+        <v>1560</v>
       </c>
       <c r="F106" t="n">
-        <v>510</v>
+        <v>465</v>
       </c>
       <c r="G106" t="n">
-        <v>780</v>
+        <v>300</v>
       </c>
       <c r="H106" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>1980</v>
+        <v>200</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>upsAccent</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S106" t="n">
@@ -8324,51 +8324,47 @@
       <c r="T106" t="n">
         <v>6</v>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>4 sections: rectifier/inverter/static switch/battery interface</t>
-        </is>
-      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HMI touchscreen</t>
+          <t>CHW supply</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-1237</v>
+        <v>-1000</v>
       </c>
       <c r="E107" t="n">
-        <v>1650</v>
+        <v>300</v>
       </c>
       <c r="F107" t="n">
-        <v>528</v>
+        <v>-500</v>
       </c>
       <c r="G107" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
@@ -8385,14 +8381,14 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S107" t="n">
@@ -8406,42 +8402,42 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELC-001</t>
+          <t>ACL-002</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Top cable duct</t>
+          <t>CHW return</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E108" t="n">
-        <v>2210</v>
+        <v>300</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="G108" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L108" t="n">
         <v>1</v>
@@ -8458,14 +8454,14 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>upsAccent</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S108" t="n">
@@ -8484,7 +8480,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vent band</t>
+          <t>Lineup body</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8496,19 +8492,19 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>180</v>
+        <v>1067</v>
       </c>
       <c r="F109" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="H109" t="n">
-        <v>15</v>
+        <v>991</v>
       </c>
       <c r="I109" t="n">
-        <v>220</v>
+        <v>2134</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8538,7 +8534,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>upsBody</t>
         </is>
       </c>
       <c r="S109" t="n">
@@ -8552,12 +8548,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lineup body</t>
+          <t>Cabinet doors</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8566,22 +8562,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>-1237</v>
       </c>
       <c r="E110" t="n">
-        <v>985</v>
+        <v>1040</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="G110" t="n">
-        <v>5600</v>
+        <v>780</v>
       </c>
       <c r="H110" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="I110" t="n">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8590,7 +8586,7 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -8598,7 +8594,7 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -8611,7 +8607,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>upsBody</t>
+          <t>upsAccent</t>
         </is>
       </c>
       <c r="S110" t="n">
@@ -8620,17 +8616,21 @@
       <c r="T110" t="n">
         <v>6</v>
       </c>
-      <c r="U110" t="inlineStr"/>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>4 sections: rectifier/inverter/static switch/battery interface</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cabinet doors</t>
+          <t>HMI touchscreen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8639,22 +8639,22 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-2330</v>
+        <v>-1237</v>
       </c>
       <c r="E111" t="n">
-        <v>960</v>
+        <v>1650</v>
       </c>
       <c r="F111" t="n">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="G111" t="n">
-        <v>880</v>
+        <v>340</v>
       </c>
       <c r="H111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I111" t="n">
-        <v>1820</v>
+        <v>220</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>upsAccent</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S111" t="n">
@@ -8693,21 +8693,17 @@
       <c r="T111" t="n">
         <v>6</v>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>6-frame lineup</t>
-        </is>
-      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>Top cable duct</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8716,22 +8712,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-2330</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>1560</v>
+        <v>2210</v>
       </c>
       <c r="F112" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>360</v>
+        <v>3300</v>
       </c>
       <c r="H112" t="n">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="I112" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -8761,7 +8757,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>upsAccent</t>
         </is>
       </c>
       <c r="S112" t="n">
@@ -8775,7 +8771,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ELC-002</t>
+          <t>ELC-001</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8792,19 +8788,19 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F113" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G113" t="n">
-        <v>5500</v>
+        <v>3200</v>
       </c>
       <c r="H113" t="n">
         <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -8848,42 +8844,42 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MEC-003</t>
+          <t>ELC-002</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Evaporator barrel</t>
+          <t>Lineup body</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>850</v>
+        <v>985</v>
       </c>
       <c r="F114" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1970</v>
       </c>
       <c r="J114" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>1</v>
@@ -8907,7 +8903,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>upsBody</t>
         </is>
       </c>
       <c r="S114" t="n">
@@ -8916,54 +8912,50 @@
       <c r="T114" t="n">
         <v>6</v>
       </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>Lower shell — chilled water side</t>
-        </is>
-      </c>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MEC-003</t>
+          <t>ELC-002</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Condenser barrel</t>
+          <t>Cabinet doors</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>-2330</v>
       </c>
       <c r="E115" t="n">
-        <v>2000</v>
+        <v>960</v>
       </c>
       <c r="F115" t="n">
-        <v>-300</v>
+        <v>500</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1820</v>
       </c>
       <c r="J115" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -8971,7 +8963,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -8984,7 +8976,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>upsAccent</t>
         </is>
       </c>
       <c r="S115" t="n">
@@ -8995,49 +8987,49 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>Upper shell — condenser water side</t>
+          <t>6-frame lineup</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MEC-003</t>
+          <t>ELC-002</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Waterbox A</t>
+          <t>HMI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-2400</v>
+        <v>-2330</v>
       </c>
       <c r="E116" t="n">
-        <v>850</v>
+        <v>1560</v>
       </c>
       <c r="F116" t="n">
-        <v>300</v>
+        <v>518</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="J116" t="n">
-        <v>1520</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -9061,7 +9053,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>screenDark</t>
         </is>
       </c>
       <c r="S116" t="n">
@@ -9075,42 +9067,42 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MEC-003</t>
+          <t>ELC-002</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Waterbox B</t>
+          <t>Vent band</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>850</v>
+        <v>170</v>
       </c>
       <c r="F117" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J117" t="n">
-        <v>1520</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>1</v>
@@ -9134,7 +9126,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S117" t="n">
@@ -9153,22 +9145,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Compressor volute</t>
+          <t>Evaporator barrel</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>2700</v>
+        <v>850</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -9180,10 +9172,10 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>1100</v>
+        <v>1450</v>
       </c>
       <c r="K118" t="n">
-        <v>700</v>
+        <v>4500</v>
       </c>
       <c r="L118" t="n">
         <v>1</v>
@@ -9207,7 +9199,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S118" t="n">
@@ -9218,7 +9210,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>Centrifugal compressor between shells</t>
+          <t>Lower shell — chilled water side</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9222,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Drive motor</t>
+          <t>Condenser barrel</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9239,13 +9231,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>2650</v>
+        <v>2000</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -9257,10 +9249,10 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>850</v>
+        <v>1350</v>
       </c>
       <c r="K119" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
@@ -9284,7 +9276,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S119" t="n">
@@ -9293,7 +9285,11 @@
       <c r="T119" t="n">
         <v>6</v>
       </c>
-      <c r="U119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Upper shell — condenser water side</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9303,19 +9299,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Suction elbow</t>
+          <t>Waterbox A</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>-200</v>
+        <v>-2400</v>
       </c>
       <c r="E120" t="n">
-        <v>2450</v>
+        <v>850</v>
       </c>
       <c r="F120" t="n">
         <v>300</v>
@@ -9330,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>700</v>
+        <v>1520</v>
       </c>
       <c r="K120" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="L120" t="n">
         <v>1</v>
@@ -9357,7 +9353,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S120" t="n">
@@ -9376,22 +9372,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CHW nozzles</t>
+          <t>Waterbox B</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-1400</v>
+        <v>2400</v>
       </c>
       <c r="E121" t="n">
-        <v>1900</v>
+        <v>850</v>
       </c>
       <c r="F121" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -9403,13 +9399,13 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K121" t="n">
         <v>350</v>
       </c>
-      <c r="K121" t="n">
-        <v>700</v>
-      </c>
       <c r="L121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -9417,7 +9413,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -9430,7 +9426,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S121" t="n">
@@ -9439,11 +9435,7 @@
       <c r="T121" t="n">
         <v>6</v>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Chilled water in/out</t>
-        </is>
-      </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9453,7 +9445,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CDW nozzles</t>
+          <t>Compressor volute</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -9462,13 +9454,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>-1400</v>
+        <v>900</v>
       </c>
       <c r="E122" t="n">
-        <v>2950</v>
+        <v>2700</v>
       </c>
       <c r="F122" t="n">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -9480,13 +9472,13 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="K122" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -9494,7 +9486,7 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -9507,7 +9499,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S122" t="n">
@@ -9518,7 +9510,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>Condenser water in/out</t>
+          <t>Centrifugal compressor between shells</t>
         </is>
       </c>
     </row>
@@ -9530,38 +9522,38 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Control panel</t>
+          <t>Drive motor</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-2100</v>
+        <v>2200</v>
       </c>
       <c r="E123" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>850</v>
+      </c>
+      <c r="K123" t="n">
         <v>1500</v>
       </c>
-      <c r="F123" t="n">
-        <v>-900</v>
-      </c>
-      <c r="G123" t="n">
-        <v>800</v>
-      </c>
-      <c r="H123" t="n">
-        <v>300</v>
-      </c>
-      <c r="I123" t="n">
-        <v>1600</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
@@ -9584,7 +9576,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>pdu</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S123" t="n">
@@ -9598,42 +9590,42 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MEC-006</t>
+          <t>MEC-003</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Inertia base</t>
+          <t>Suction elbow</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E124" t="n">
-        <v>100</v>
+        <v>2450</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G124" t="n">
-        <v>2030</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L124" t="n">
         <v>1</v>
@@ -9657,7 +9649,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>gensetDark</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="S124" t="n">
@@ -9671,27 +9663,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MEC-006</t>
+          <t>MEC-003</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Motor</t>
+          <t>CHW nozzles</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-450</v>
+        <v>-1400</v>
       </c>
       <c r="E125" t="n">
-        <v>650</v>
+        <v>1900</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -9703,13 +9695,13 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="K125" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -9717,7 +9709,7 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -9730,7 +9722,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>chiller</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S125" t="n">
@@ -9739,32 +9731,36 @@
       <c r="T125" t="n">
         <v>6</v>
       </c>
-      <c r="U125" t="inlineStr"/>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Chilled water in/out</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MEC-006</t>
+          <t>MEC-003</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Coupling guard</t>
+          <t>CDW nozzles</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>200</v>
+        <v>-1400</v>
       </c>
       <c r="E126" t="n">
-        <v>650</v>
+        <v>2950</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -9776,13 +9772,13 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K126" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -9790,7 +9786,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -9803,7 +9799,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>genset</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S126" t="n">
@@ -9812,47 +9808,51 @@
       <c r="T126" t="n">
         <v>6</v>
       </c>
-      <c r="U126" t="inlineStr"/>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Condenser water in/out</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MEC-006</t>
+          <t>MEC-003</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Volute casing</t>
+          <t>Control panel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>600</v>
+        <v>-2100</v>
       </c>
       <c r="E127" t="n">
-        <v>550</v>
+        <v>1500</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="J127" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>1</v>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>pdu</t>
         </is>
       </c>
       <c r="S127" t="n">
@@ -9895,37 +9895,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Suction pipe</t>
+          <t>Inertia base</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J128" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>gensetDark</t>
         </is>
       </c>
       <c r="S128" t="n">
@@ -9968,19 +9968,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Discharge pipe</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>cyl</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>600</v>
+        <v>-450</v>
       </c>
       <c r="E129" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -9995,10 +9995,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>200</v>
+        <v>550</v>
       </c>
       <c r="K129" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L129" t="n">
         <v>1</v>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>chiller</t>
         </is>
       </c>
       <c r="S129" t="n">
@@ -10036,42 +10036,42 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LCL-004</t>
+          <t>MEC-006</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Coupling guard</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E130" t="n">
-        <v>1132</v>
+        <v>650</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>2265</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L130" t="n">
         <v>1</v>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>cdu</t>
+          <t>genset</t>
         </is>
       </c>
       <c r="S130" t="n">
@@ -10109,42 +10109,42 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LCL-004</t>
+          <t>MEC-006</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Front louver</t>
+          <t>Volute casing</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E131" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="F131" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>chillerCoil</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S131" t="n">
@@ -10182,27 +10182,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LCL-004</t>
+          <t>MEC-006</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Internal fan column</t>
+          <t>Suction pipe</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="E132" t="n">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="F132" t="n">
-        <v>-350</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -10214,24 +10214,24 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>420</v>
+        <v>250</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="L132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>x</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
@@ -10241,45 +10241,41 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>fanBlade</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>7</v>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>Vertical stack of fans pulling air through the HX</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LCL-004</t>
+          <t>MEC-006</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Coolant supply</t>
+          <t>Discharge pipe</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>cyl</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>-140</v>
+        <v>600</v>
       </c>
       <c r="E133" t="n">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="F133" t="n">
-        <v>-660</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -10291,10 +10287,10 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="K133" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="L133" t="n">
         <v>1</v>
@@ -10311,14 +10307,14 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>pipeSupply</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S133" t="n">
@@ -10337,37 +10333,37 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Coolant return</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>cylH</t>
+          <t>box</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>300</v>
+        <v>1132</v>
       </c>
       <c r="F134" t="n">
-        <v>-660</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>2265</v>
       </c>
       <c r="J134" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
@@ -10384,14 +10380,14 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>pipeReturn</t>
+          <t>cdu</t>
         </is>
       </c>
       <c r="S134" t="n">
@@ -10405,12 +10401,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ACL-001</t>
+          <t>LCL-004</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Front louver</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10422,19 +10418,19 @@
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>998</v>
+        <v>1100</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="G135" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="H135" t="n">
-        <v>1100</v>
+        <v>18</v>
       </c>
       <c r="I135" t="n">
-        <v>1996</v>
+        <v>1900</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10464,7 +10460,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>crah</t>
+          <t>chillerCoil</t>
         </is>
       </c>
       <c r="S135" t="n">
@@ -10478,56 +10474,56 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ACL-001</t>
+          <t>LCL-004</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Front discharge grille</t>
+          <t>Internal fan column</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>fan</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="F136" t="n">
-        <v>558</v>
+        <v>-350</v>
       </c>
       <c r="G136" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>y</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -10537,56 +10533,60 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>fanBlade</t>
         </is>
       </c>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" t="n">
-        <v>6</v>
-      </c>
-      <c r="U136" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Vertical stack of fans pulling air through the HX</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ACL-001</t>
+          <t>LCL-004</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rear intake grille</t>
+          <t>Coolant supply</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>-140</v>
       </c>
       <c r="E137" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F137" t="n">
-        <v>-558</v>
+        <v>-660</v>
       </c>
       <c r="G137" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
@@ -10603,14 +10603,14 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>crahDark</t>
+          <t>pipeSupply</t>
         </is>
       </c>
       <c r="S137" t="n">
@@ -10624,42 +10624,42 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ACL-001</t>
+          <t>LCL-004</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>Coolant return</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>cylH</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E138" t="n">
-        <v>1780</v>
+        <v>300</v>
       </c>
       <c r="F138" t="n">
-        <v>560</v>
+        <v>-660</v>
       </c>
       <c r="G138" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="L138" t="n">
         <v>1</v>
@@ -10676,14 +10676,14 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>screenDark</t>
+          <t>pipeReturn</t>
         </is>
       </c>
       <c r="S138" t="n">
@@ -10702,70 +10702,362 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>998</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>600</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>crah</t>
+        </is>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>6</v>
+      </c>
+      <c r="U139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Front discharge grille</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F140" t="n">
+        <v>558</v>
+      </c>
+      <c r="G140" t="n">
+        <v>540</v>
+      </c>
+      <c r="H140" t="n">
+        <v>18</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>crahDark</t>
+        </is>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>6</v>
+      </c>
+      <c r="U140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Rear intake grille</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-558</v>
+      </c>
+      <c r="G141" t="n">
+        <v>540</v>
+      </c>
+      <c r="H141" t="n">
+        <v>18</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1700</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>crahDark</t>
+        </is>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>6</v>
+      </c>
+      <c r="U141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HMI</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>box</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1780</v>
+      </c>
+      <c r="F142" t="n">
+        <v>560</v>
+      </c>
+      <c r="G142" t="n">
+        <v>220</v>
+      </c>
+      <c r="H142" t="n">
+        <v>12</v>
+      </c>
+      <c r="I142" t="n">
+        <v>140</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>screenDark</t>
+        </is>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>6</v>
+      </c>
+      <c r="U142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ACL-001</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>CHW stubs</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>cylH</t>
         </is>
       </c>
-      <c r="D139" t="n">
+      <c r="D143" t="n">
         <v>-120</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E143" t="n">
         <v>250</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F143" t="n">
         <v>-580</v>
       </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
         <v>60</v>
       </c>
-      <c r="K139" t="n">
+      <c r="K143" t="n">
         <v>250</v>
       </c>
-      <c r="L139" t="n">
+      <c r="L143" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N139" t="n">
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
         <v>240</v>
       </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
         <v>90</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="inlineStr">
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="inlineStr">
         <is>
           <t>pipeSupply</t>
         </is>
       </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>6</v>
-      </c>
-      <c r="U139" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>6</v>
+      </c>
+      <c r="U143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
